--- a/Server/NewServer/bin/commonconfig/setting/master_gift.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/master_gift.xlsx
@@ -62,7 +62,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟等级提升给徒弟的邮件的邮件</t>
+          <t>Mail to the apprentice when they level up; mail </t>
         </r>
         <r>
           <rPr>
@@ -116,7 +116,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟等级提升给师傅的邮件的邮件</t>
+          <t>Mail to the mentor when the apprentice levels up; mail </t>
         </r>
         <r>
           <rPr>
@@ -170,7 +170,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>种祝贺的金钱消耗</t>
+          <t> congratulation options and their currency costs</t>
         </r>
       </text>
     </comment>
@@ -215,7 +215,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>师徒祝贺徒弟，发送给师傅的礼包邮件</t>
+          <t>Gift mail to the mentor when mentor and apprentice congratulate the apprentice; mail </t>
         </r>
         <r>
           <rPr>
@@ -269,7 +269,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>师徒祝贺徒弟，发送给徒弟的礼包邮件</t>
+          <t>Gift mail to the apprentice when mentor and apprentice congratulate the apprentice; mail </t>
         </r>
         <r>
           <rPr>
@@ -323,7 +323,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟恭喜师傅，发送给师傅的礼包邮件</t>
+          <t>Gift mail to the mentor when the apprentice congratulates the mentor; mail </t>
         </r>
         <r>
           <rPr>
@@ -377,7 +377,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟恭喜师傅，发送给徒弟的礼包邮件</t>
+          <t>Gift mail to the apprentice when the apprentice congratulates the mentor; mail </t>
         </r>
         <r>
           <rPr>
@@ -431,7 +431,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>同门祝贺，发送给祝贺者自己的礼包邮件</t>
+          <t>Gift mail to the congratulating fellow apprentice; mail </t>
         </r>
         <r>
           <rPr>
@@ -485,7 +485,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>同门祝贺，发送给需要祝贺目标的礼包邮件</t>
+          <t>Gift mail to the congratulated fellow apprentice; mail </t>
         </r>
         <r>
           <rPr>
@@ -549,7 +549,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟等级提升给徒弟的邮件的邮件</t>
+          <t>Mail to the apprentice when they level up; mail </t>
         </r>
         <r>
           <rPr>
@@ -603,7 +603,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟等级提升给师傅的邮件的邮件</t>
+          <t>Mail to the mentor when the apprentice levels up; mail </t>
         </r>
         <r>
           <rPr>
@@ -657,7 +657,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>种祝贺的金钱消耗</t>
+          <t> congratulation options and their currency costs</t>
         </r>
       </text>
     </comment>
@@ -702,7 +702,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>师徒祝贺徒弟，发送给师傅的礼包邮件</t>
+          <t>Gift mail to the mentor when mentor and apprentice congratulate the apprentice; mail </t>
         </r>
         <r>
           <rPr>
@@ -756,7 +756,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>师徒祝贺徒弟，发送给徒弟的礼包邮件</t>
+          <t>Gift mail to the apprentice when mentor and apprentice congratulate the apprentice; mail </t>
         </r>
         <r>
           <rPr>
@@ -810,7 +810,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟恭喜师傅，发送给师傅的礼包邮件</t>
+          <t>Gift mail to the mentor when the apprentice congratulates the mentor; mail </t>
         </r>
         <r>
           <rPr>
@@ -864,7 +864,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>徒弟恭喜师傅，发送给徒弟的礼包邮件</t>
+          <t>Gift mail to the apprentice when the apprentice congratulates the mentor; mail </t>
         </r>
         <r>
           <rPr>
@@ -918,7 +918,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>同门祝贺，发送给祝贺者自己的礼包邮件</t>
+          <t>Gift mail to the congratulating fellow apprentice; mail </t>
         </r>
         <r>
           <rPr>
@@ -972,7 +972,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>同门祝贺，发送给需要祝贺目标的礼包邮件</t>
+          <t>Gift mail to the congratulated fellow apprentice; mail </t>
         </r>
         <r>
           <rPr>
